--- a/docs/test-cases.xlsx
+++ b/docs/test-cases.xlsx
@@ -4004,7 +4004,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4170,20 +4170,86 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
+          <t>2026-10-23 22:26</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>TC-B02/B03/B05/B07/B08、TC-C05/C09、TC-D03/D07、TC-E08/E11、TC-F05/F06、TC-G07</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>通过 14 条，失败 0 条</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>scripts/test-cases-api.ps1；logs/test-cases-api.log</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-23 22:27</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>TC-A01/A02/A03、TC-B01/B04/B06、TC-C01/C03/C04、TC-E01/E03/E06/E07、TC-G01/G04</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>通过 9 条（补 @Valid 依赖后回归）</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>scripts/acceptance.ps1</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-23 22:27</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>TC-H01/H02（备份与日志轮转属于运维）</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>备份 438.5KB 成功；日志轮转 12MB→.1.log 验证通过</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>scripts/housekeeping.ps1 试跑</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
           <t>待人工</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>TC-I02/I03/I04/I05/I06/I07、TC-A04/A06/A07、TC-B03/B05、TC-C05、TC-E05</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>TC-I02/I03/I04/I05/I06/I07、TC-A04/A06/A07、TC-E05</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>未执行（需浏览器人工验证）</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>按本文步骤在浏览器里点一遍，把结果填到 Excel 的「实际结果」列</t>
         </is>
